--- a/niumee/Niumee_Zenoti_Missing_Prices.xlsx
+++ b/niumee/Niumee_Zenoti_Missing_Prices.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prices to set in Zenoti" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prices to confirm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -62,12 +68,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00EEF3FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,13 +112,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,27 +485,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zenoti services with no price set</t>
+          <t>Niumee: services with no price in Zenoti</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>32 services. Nima reads prices from Zenoti, so it cannot quote these and has to defer to reception. Setting the price in Zenoti is picked up automatically, no further work needed on our side.</t>
+          <t>26 services. The assistant reads prices from Zenoti, so for these it cannot quote anything and has to pass the client to reception. We have pre-filled our assumption in column D so you only need to confirm or correct. Once set in Zenoti the assistant picks them up automatically.</t>
         </is>
       </c>
     </row>
@@ -508,22 +513,22 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Service (exact Zenoti name)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Service (exact Zenoti name)</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Duration (min)</t>
+          <t>Price (EUR)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Price to set (EUR)</t>
+          <t>Our assumption - confirm or correct</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -535,546 +540,445 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Brow &amp; Lash</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Brow &amp; Lash test patch</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>A. Semi-permanent makeup: consultations, touch-ups and follow-ups</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Brow &amp; Lash</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Velashape Consultation</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
+          <t>Phi Brows  1 month Touch Up - by Mehmet</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>3D Scan Med Aesthetic Analysis</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Phi Consultation with Mehmet</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Beauty Consultation - by Beautician</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
+          <t>Rebrow by Mel - SPM Touch Up 4-6 Weeks</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CelluSmooth Consultation</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Semi permanent 4 - 6 week touch up</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Hair Extensions Consultation with Alberto</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
+          <t>Semi permanent makeup consultation</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Open  Weekend  - Hair Transplant Consultation</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SPM eyebrow follow up by Ilona</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>PH Resurfacing Treatment Consultation</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
+          <t>SPM eyeliner follow up by Ilona</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Consultations</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care expert consultation</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Dermapen Microneedling &amp; RF</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Dermapen Consultation</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SPM lip follow up by Ilona</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Dermapen Microneedling &amp; RF</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>RF Consultation</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
+          <t>B. Consultations</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Hair Salon</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Hair Extensions Application Fee</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
+          <t>Velashape Consultation</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>IV Drips</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>IV drips Consultation</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>3D Scan Med Aesthetic Analysis</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Laser Hair Removal</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>FREE Consultation and test patch with nurses</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
+          <t>Beauty Consultation - by Beautician</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Massage &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Sports Therapy session  (45 mins)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>CelluSmooth Consultation</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Massage &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Sports Therapy Sponsored session</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
+          <t>Hair Extensions Consultation with Alberto</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Med-Aesthetics</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Stavrou operations Hospital Fees</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Open  Weekend  - Hair Transplant Consultation</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Promo item, only live during Open Weekends - exclude from the assistant?</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Med-Aesthetics</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Filler Appointment</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
+          <t>PH Resurfacing Treatment Consultation</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Med-Aesthetics</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Skin Bleaching consultation</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Skin Care expert consultation</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Phi Brows  1 month Touch Up - by Mehmet</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
+          <t>RF Consultation</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Phi Consultation with Mehmet</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>IV drips Consultation</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Rebrow by Mel - SPM Touch Up 4-6 Weeks</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Skin Bleaching consultation</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Semi permanent 4 - 6 week touch up</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Semi permanent makeup consultation</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Slimming consultation</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Standard EUR50 consultation? (confirm or give the specialist price)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>SPM Clinic Fee</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
+          <t>C. Other</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>SPM eyebrow follow up by Ilona</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
+          <t>Brow &amp; Lash test patch</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Free? (laser test patches are free, is this the same)</t>
+        </is>
+      </c>
       <c r="E31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>SPM eyeliner follow up by Ilona</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Hair Extensions Application Fee</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Varies with the work done? (quote at consultation)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Semi-permanent makeup</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>SPM lip follow up by Ilona</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
+          <t>Sports Therapy session  (45 mins)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Teen +</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Teen + Free consultation + Test Patch with Nurse</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Sports Therapy Sponsored session</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Not charged to the client? (internal/sponsored)</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Weightloss &amp;Cellulite Treatments</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Sculptpro Free Consultation &amp; Trial session</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
+          <t>Filler Appointment</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Priced at the appointment by the doctor? (product dependent)</t>
+        </is>
+      </c>
       <c r="E35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Weightloss &amp;Cellulite Treatments</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Slimming consultation</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Weightloss &amp;Cellulite Treatments</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Weight loss (HCG) follow up</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
